--- a/IMT.xlsx
+++ b/IMT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sourav\Desktop\IMT_games\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{377C1F20-6403-482D-B5E4-ADE7DEF8CBC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87975610-8C91-4FD3-957D-0C293795D391}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -66,9 +66,6 @@
     <t>Authorized Company</t>
   </si>
   <si>
-    <t>80% of dentists recommend BrightSmile toothpaste.</t>
-  </si>
-  <si>
     <t>False Attribution</t>
   </si>
   <si>
@@ -79,6 +76,9 @@
   </si>
   <si>
     <t>Only positive evidence is presented while contradictory evidence is ignored.</t>
+  </si>
+  <si>
+    <t>Colgate's "9 out of 10 dentists recommend Colgate"</t>
   </si>
 </sst>
 </file>
@@ -446,13 +446,13 @@
         <v>10</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>16</v>
-      </c>
     </row>
-    <row r="2" spans="1:10" s="3" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" s="3" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -463,7 +463,7 @@
         <v>12</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>0</v>
@@ -475,13 +475,13 @@
         <v>2</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/IMT.xlsx
+++ b/IMT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sourav\Desktop\IMT_games\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87975610-8C91-4FD3-957D-0C293795D391}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B028FED6-D7FF-4746-B99D-276D5DFF97AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,16 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
-  <si>
-    <t>Cherry Picking</t>
-  </si>
-  <si>
-    <t>Fabrication</t>
-  </si>
-  <si>
-    <t>Exaggeration</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>ID</t>
   </si>
@@ -66,9 +57,6 @@
     <t>Authorized Company</t>
   </si>
   <si>
-    <t>False Attribution</t>
-  </si>
-  <si>
     <t>Correct_Answer</t>
   </si>
   <si>
@@ -79,6 +67,21 @@
   </si>
   <si>
     <t>Colgate's "9 out of 10 dentists recommend Colgate"</t>
+  </si>
+  <si>
+    <t>Exaggerated Truthful Information</t>
+  </si>
+  <si>
+    <t>Fabricated Disinformation</t>
+  </si>
+  <si>
+    <t>Consequential Disinformation</t>
+  </si>
+  <si>
+    <t>Fabricated Misinformation</t>
+  </si>
+  <si>
+    <t>Cherry Picked Misinformation</t>
   </si>
 </sst>
 </file>
@@ -416,72 +419,76 @@
   <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="3" max="3" width="17.109375" customWidth="1"/>
+    <col min="4" max="4" width="18.21875" customWidth="1"/>
+    <col min="7" max="7" width="24.5546875" customWidth="1"/>
+    <col min="8" max="8" width="23.109375" customWidth="1"/>
     <col min="9" max="9" width="16.44140625" customWidth="1"/>
     <col min="10" max="10" width="22.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="J1" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="3" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" s="3" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/IMT.xlsx
+++ b/IMT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sourav\Desktop\IMT_games\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B028FED6-D7FF-4746-B99D-276D5DFF97AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21E0B4B0-8922-4EB1-9251-E01D1C8DD610}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
   <si>
     <t>ID</t>
   </si>
@@ -70,9 +70,6 @@
   </si>
   <si>
     <t>Exaggerated Truthful Information</t>
-  </si>
-  <si>
-    <t>Fabricated Disinformation</t>
   </si>
   <si>
     <t>Consequential Disinformation</t>
@@ -473,16 +470,16 @@
         <v>13</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>14</v>
